--- a/public/plantilla-inspeccion-ambiental.xlsx
+++ b/public/plantilla-inspeccion-ambiental.xlsx
@@ -15,6 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="hh:mm"/>
+  </numFmts>
   <fonts count="20">
     <font>
       <name val="Calibri"/>
@@ -554,19 +557,19 @@
     <xf numFmtId="4" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -615,7 +618,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -668,7 +671,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">

--- a/public/plantilla-inspeccion-ambiental.xlsx
+++ b/public/plantilla-inspeccion-ambiental.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="9" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inspección Ambiental" sheetId="1" state="visible" r:id="rId1"/>
@@ -1226,9 +1226,9 @@
     <col width="15.77734375" customWidth="1" style="27" min="8" max="8"/>
     <col width="10" customWidth="1" style="27" min="9" max="9"/>
     <col width="15.77734375" customWidth="1" style="27" min="10" max="10"/>
-    <col width="12" customWidth="1" style="27" min="11" max="11"/>
-    <col width="15.77734375" customWidth="1" style="27" min="12" max="12"/>
-    <col width="8.88671875" customWidth="1" style="27" min="13" max="16384"/>
+    <col width="20.78" customWidth="1" style="27" min="11" max="12"/>
+    <col width="8.88671875" customWidth="1" style="27" min="13" max="30"/>
+    <col width="8.88671875" customWidth="1" style="27" min="31" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="40.05" customHeight="1" s="27">

--- a/public/plantilla-inspeccion-ambiental.xlsx
+++ b/public/plantilla-inspeccion-ambiental.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inspección Ambiental" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,9 +16,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="hh:mm"/>
+    <numFmt numFmtId="164" formatCode="hh:mm"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -162,6 +162,10 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="17">
@@ -529,7 +533,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -560,7 +564,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -636,7 +640,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -757,6 +761,56 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1219,6 +1273,7 @@
   <cols>
     <col width="12.77734375" customWidth="1" style="27" min="1" max="1"/>
     <col width="13" customWidth="1" style="27" min="2" max="3"/>
+    <col width="13" customWidth="1" style="27" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="27" min="4" max="4"/>
     <col width="10" customWidth="1" style="27" min="5" max="5"/>
     <col width="15.77734375" customWidth="1" style="27" min="6" max="6"/>
@@ -1386,16 +1441,16 @@
         </is>
       </c>
       <c r="B11" s="22" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="25" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="25" t="n"/>
-      <c r="G11" s="25" t="n"/>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="25" t="n"/>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="25" t="n"/>
-      <c r="L11" s="22" t="n"/>
+      <c r="C11" s="97" t="n"/>
+      <c r="D11" s="98" t="n"/>
+      <c r="E11" s="98" t="n"/>
+      <c r="F11" s="98" t="n"/>
+      <c r="G11" s="98" t="n"/>
+      <c r="H11" s="98" t="n"/>
+      <c r="I11" s="98" t="n"/>
+      <c r="J11" s="98" t="n"/>
+      <c r="K11" s="98" t="n"/>
+      <c r="L11" s="99" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="27">
       <c r="A12" s="88" t="inlineStr">
@@ -1404,20 +1459,20 @@
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="22" t="n"/>
+      <c r="C12" s="97" t="n"/>
+      <c r="D12" s="98" t="n"/>
+      <c r="E12" s="98" t="n"/>
+      <c r="F12" s="98" t="n"/>
+      <c r="G12" s="99" t="n"/>
       <c r="H12" s="88" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="I12" s="22" t="n"/>
-      <c r="J12" s="24" t="n"/>
-      <c r="K12" s="25" t="n"/>
-      <c r="L12" s="22" t="n"/>
+      <c r="J12" s="97" t="n"/>
+      <c r="K12" s="98" t="n"/>
+      <c r="L12" s="99" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="27">
       <c r="A13" s="88" t="inlineStr">
@@ -1426,24 +1481,24 @@
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="22" t="n"/>
+      <c r="C13" s="100" t="n"/>
+      <c r="D13" s="99" t="n"/>
       <c r="E13" s="88" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
       <c r="F13" s="22" t="n"/>
-      <c r="G13" s="44" t="n"/>
-      <c r="H13" s="22" t="n"/>
+      <c r="G13" s="101" t="n"/>
+      <c r="H13" s="99" t="n"/>
       <c r="I13" s="88" t="inlineStr">
         <is>
           <t>Inspección N°</t>
         </is>
       </c>
       <c r="J13" s="22" t="n"/>
-      <c r="K13" s="32" t="n"/>
-      <c r="L13" s="22" t="n"/>
+      <c r="K13" s="102" t="n"/>
+      <c r="L13" s="99" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="27">
       <c r="A14" s="88" t="inlineStr">
@@ -1452,20 +1507,20 @@
         </is>
       </c>
       <c r="B14" s="22" t="n"/>
-      <c r="C14" s="24" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="25" t="n"/>
-      <c r="F14" s="25" t="n"/>
-      <c r="G14" s="22" t="n"/>
+      <c r="C14" s="97" t="n"/>
+      <c r="D14" s="98" t="n"/>
+      <c r="E14" s="98" t="n"/>
+      <c r="F14" s="98" t="n"/>
+      <c r="G14" s="99" t="n"/>
       <c r="H14" s="88" t="inlineStr">
         <is>
           <t>Frente o zona</t>
         </is>
       </c>
       <c r="I14" s="22" t="n"/>
-      <c r="J14" s="24" t="n"/>
-      <c r="K14" s="25" t="n"/>
-      <c r="L14" s="22" t="n"/>
+      <c r="J14" s="97" t="n"/>
+      <c r="K14" s="98" t="n"/>
+      <c r="L14" s="99" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1" s="27">
       <c r="A15" s="88" t="inlineStr">
@@ -1474,24 +1529,24 @@
         </is>
       </c>
       <c r="B15" s="22" t="n"/>
-      <c r="C15" s="32" t="n"/>
-      <c r="D15" s="22" t="n"/>
+      <c r="C15" s="102" t="n"/>
+      <c r="D15" s="99" t="n"/>
       <c r="E15" s="88" t="inlineStr">
         <is>
           <t>Condición del clima</t>
         </is>
       </c>
       <c r="F15" s="22" t="n"/>
-      <c r="G15" s="32" t="n"/>
-      <c r="H15" s="22" t="n"/>
+      <c r="G15" s="102" t="n"/>
+      <c r="H15" s="99" t="n"/>
       <c r="I15" s="88" t="inlineStr">
         <is>
           <t>Acompañó</t>
         </is>
       </c>
       <c r="J15" s="22" t="n"/>
-      <c r="K15" s="24" t="n"/>
-      <c r="L15" s="22" t="n"/>
+      <c r="K15" s="97" t="n"/>
+      <c r="L15" s="99" t="n"/>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="27">
       <c r="A16" s="77" t="inlineStr">
@@ -1546,16 +1601,16 @@
       <c r="L17" s="21" t="n"/>
     </row>
     <row r="18" ht="25.95" customHeight="1" s="27">
-      <c r="A18" s="41" t="n">
+      <c r="A18" s="103" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="104" t="inlineStr">
         <is>
           <t>Residuos</t>
         </is>
       </c>
       <c r="C18" s="18" t="n"/>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="104" t="inlineStr">
         <is>
           <t>Puntos ecológicos y canecas rotulados, con tapa y sin desbordar</t>
         </is>
@@ -1564,22 +1619,22 @@
       <c r="F18" s="17" t="n"/>
       <c r="G18" s="17" t="n"/>
       <c r="H18" s="18" t="n"/>
-      <c r="I18" s="41" t="n"/>
-      <c r="J18" s="18" t="n"/>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="18" t="n"/>
+      <c r="I18" s="105" t="n"/>
+      <c r="J18" s="106" t="n"/>
+      <c r="K18" s="107" t="n"/>
+      <c r="L18" s="106" t="n"/>
     </row>
     <row r="19" ht="25.95" customHeight="1" s="27">
-      <c r="A19" s="41" t="n">
+      <c r="A19" s="103" t="n">
         <v>2</v>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="104" t="inlineStr">
         <is>
           <t>Residuos</t>
         </is>
       </c>
       <c r="C19" s="18" t="n"/>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="104" t="inlineStr">
         <is>
           <t>Residuos separados por tipo (aprovechables, ordinarios y peligrosos)</t>
         </is>
@@ -1588,22 +1643,22 @@
       <c r="F19" s="17" t="n"/>
       <c r="G19" s="17" t="n"/>
       <c r="H19" s="18" t="n"/>
-      <c r="I19" s="41" t="n"/>
-      <c r="J19" s="18" t="n"/>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="18" t="n"/>
-    </row>
-    <row r="20" ht="25.95" customHeight="1" s="27">
-      <c r="A20" s="41" t="n">
+      <c r="I19" s="105" t="n"/>
+      <c r="J19" s="106" t="n"/>
+      <c r="K19" s="107" t="n"/>
+      <c r="L19" s="106" t="n"/>
+    </row>
+    <row r="20" ht="29" customHeight="1" s="27">
+      <c r="A20" s="103" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="104" t="inlineStr">
         <is>
           <t>Residuos</t>
         </is>
       </c>
       <c r="C20" s="18" t="n"/>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="104" t="inlineStr">
         <is>
           <t>Escombros acopiados en el sitio autorizado, sin invadir el espacio público</t>
         </is>
@@ -1612,22 +1667,22 @@
       <c r="F20" s="17" t="n"/>
       <c r="G20" s="17" t="n"/>
       <c r="H20" s="18" t="n"/>
-      <c r="I20" s="41" t="n"/>
-      <c r="J20" s="18" t="n"/>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="18" t="n"/>
+      <c r="I20" s="105" t="n"/>
+      <c r="J20" s="106" t="n"/>
+      <c r="K20" s="107" t="n"/>
+      <c r="L20" s="106" t="n"/>
     </row>
     <row r="21" ht="19.05" customHeight="1" s="27">
-      <c r="A21" s="41" t="n">
+      <c r="A21" s="103" t="n">
         <v>4</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="104" t="inlineStr">
         <is>
           <t>Residuos</t>
         </is>
       </c>
       <c r="C21" s="18" t="n"/>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="104" t="inlineStr">
         <is>
           <t>Residuos peligrosos en zona rotulada, techada y con contención</t>
         </is>
@@ -1636,22 +1691,22 @@
       <c r="F21" s="17" t="n"/>
       <c r="G21" s="17" t="n"/>
       <c r="H21" s="18" t="n"/>
-      <c r="I21" s="41" t="n"/>
-      <c r="J21" s="18" t="n"/>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="18" t="n"/>
+      <c r="I21" s="105" t="n"/>
+      <c r="J21" s="106" t="n"/>
+      <c r="K21" s="107" t="n"/>
+      <c r="L21" s="106" t="n"/>
     </row>
     <row r="22" ht="19.05" customHeight="1" s="27">
-      <c r="A22" s="41" t="n">
+      <c r="A22" s="103" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="104" t="inlineStr">
         <is>
           <t>Residuos</t>
         </is>
       </c>
       <c r="C22" s="18" t="n"/>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D22" s="104" t="inlineStr">
         <is>
           <t>Certificados y manifiestos de entrega al día</t>
         </is>
@@ -1660,22 +1715,22 @@
       <c r="F22" s="17" t="n"/>
       <c r="G22" s="17" t="n"/>
       <c r="H22" s="18" t="n"/>
-      <c r="I22" s="41" t="n"/>
-      <c r="J22" s="18" t="n"/>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="18" t="n"/>
+      <c r="I22" s="105" t="n"/>
+      <c r="J22" s="106" t="n"/>
+      <c r="K22" s="107" t="n"/>
+      <c r="L22" s="106" t="n"/>
     </row>
     <row r="23" ht="19.05" customHeight="1" s="27">
-      <c r="A23" s="41" t="n">
+      <c r="A23" s="103" t="n">
         <v>6</v>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="104" t="inlineStr">
         <is>
           <t>Agua</t>
         </is>
       </c>
       <c r="C23" s="18" t="n"/>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="104" t="inlineStr">
         <is>
           <t>Trampas de grasas y sedimentadores en funcionamiento</t>
         </is>
@@ -1684,22 +1739,22 @@
       <c r="F23" s="17" t="n"/>
       <c r="G23" s="17" t="n"/>
       <c r="H23" s="18" t="n"/>
-      <c r="I23" s="41" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="16" t="n"/>
-      <c r="L23" s="18" t="n"/>
+      <c r="I23" s="105" t="n"/>
+      <c r="J23" s="106" t="n"/>
+      <c r="K23" s="107" t="n"/>
+      <c r="L23" s="106" t="n"/>
     </row>
     <row r="24" ht="19.05" customHeight="1" s="27">
-      <c r="A24" s="41" t="n">
+      <c r="A24" s="103" t="n">
         <v>7</v>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="104" t="inlineStr">
         <is>
           <t>Agua</t>
         </is>
       </c>
       <c r="C24" s="18" t="n"/>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="104" t="inlineStr">
         <is>
           <t>Sin vertimientos de concreto, pinturas o solventes</t>
         </is>
@@ -1708,22 +1763,22 @@
       <c r="F24" s="17" t="n"/>
       <c r="G24" s="17" t="n"/>
       <c r="H24" s="18" t="n"/>
-      <c r="I24" s="41" t="n"/>
-      <c r="J24" s="18" t="n"/>
-      <c r="K24" s="16" t="n"/>
-      <c r="L24" s="18" t="n"/>
+      <c r="I24" s="105" t="n"/>
+      <c r="J24" s="106" t="n"/>
+      <c r="K24" s="107" t="n"/>
+      <c r="L24" s="106" t="n"/>
     </row>
     <row r="25" ht="19.05" customHeight="1" s="27">
-      <c r="A25" s="41" t="n">
+      <c r="A25" s="103" t="n">
         <v>8</v>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="104" t="inlineStr">
         <is>
           <t>Agua</t>
         </is>
       </c>
       <c r="C25" s="18" t="n"/>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="104" t="inlineStr">
         <is>
           <t>Uso del agua sin desperdicio ni fugas</t>
         </is>
@@ -1732,22 +1787,22 @@
       <c r="F25" s="17" t="n"/>
       <c r="G25" s="17" t="n"/>
       <c r="H25" s="18" t="n"/>
-      <c r="I25" s="41" t="n"/>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="18" t="n"/>
+      <c r="I25" s="105" t="n"/>
+      <c r="J25" s="106" t="n"/>
+      <c r="K25" s="107" t="n"/>
+      <c r="L25" s="106" t="n"/>
     </row>
     <row r="26" ht="19.05" customHeight="1" s="27">
-      <c r="A26" s="41" t="n">
+      <c r="A26" s="103" t="n">
         <v>9</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="104" t="inlineStr">
         <is>
           <t>Aire y ruido</t>
         </is>
       </c>
       <c r="C26" s="18" t="n"/>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D26" s="104" t="inlineStr">
         <is>
           <t>Vías y zonas de movimiento de tierras humedecidas</t>
         </is>
@@ -1756,22 +1811,22 @@
       <c r="F26" s="17" t="n"/>
       <c r="G26" s="17" t="n"/>
       <c r="H26" s="18" t="n"/>
-      <c r="I26" s="41" t="n"/>
-      <c r="J26" s="18" t="n"/>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="18" t="n"/>
+      <c r="I26" s="105" t="n"/>
+      <c r="J26" s="106" t="n"/>
+      <c r="K26" s="107" t="n"/>
+      <c r="L26" s="106" t="n"/>
     </row>
     <row r="27" ht="19.05" customHeight="1" s="27">
-      <c r="A27" s="41" t="n">
+      <c r="A27" s="103" t="n">
         <v>10</v>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="104" t="inlineStr">
         <is>
           <t>Aire y ruido</t>
         </is>
       </c>
       <c r="C27" s="18" t="n"/>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="104" t="inlineStr">
         <is>
           <t>Volquetas y acopios cubiertos</t>
         </is>
@@ -1780,22 +1835,22 @@
       <c r="F27" s="17" t="n"/>
       <c r="G27" s="17" t="n"/>
       <c r="H27" s="18" t="n"/>
-      <c r="I27" s="41" t="n"/>
-      <c r="J27" s="18" t="n"/>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="18" t="n"/>
+      <c r="I27" s="105" t="n"/>
+      <c r="J27" s="106" t="n"/>
+      <c r="K27" s="107" t="n"/>
+      <c r="L27" s="106" t="n"/>
     </row>
     <row r="28" ht="19.05" customHeight="1" s="27">
-      <c r="A28" s="41" t="n">
+      <c r="A28" s="103" t="n">
         <v>11</v>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="104" t="inlineStr">
         <is>
           <t>Aire y ruido</t>
         </is>
       </c>
       <c r="C28" s="18" t="n"/>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="104" t="inlineStr">
         <is>
           <t>Actividades ruidosas dentro del horario permitido</t>
         </is>
@@ -1804,22 +1859,22 @@
       <c r="F28" s="17" t="n"/>
       <c r="G28" s="17" t="n"/>
       <c r="H28" s="18" t="n"/>
-      <c r="I28" s="41" t="n"/>
-      <c r="J28" s="18" t="n"/>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="18" t="n"/>
+      <c r="I28" s="105" t="n"/>
+      <c r="J28" s="106" t="n"/>
+      <c r="K28" s="107" t="n"/>
+      <c r="L28" s="106" t="n"/>
     </row>
     <row r="29" ht="19.05" customHeight="1" s="27">
-      <c r="A29" s="41" t="n">
+      <c r="A29" s="103" t="n">
         <v>12</v>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="104" t="inlineStr">
         <is>
           <t>Aire y ruido</t>
         </is>
       </c>
       <c r="C29" s="18" t="n"/>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D29" s="104" t="inlineStr">
         <is>
           <t>Maquinaria sin humo visible</t>
         </is>
@@ -1828,22 +1883,22 @@
       <c r="F29" s="17" t="n"/>
       <c r="G29" s="17" t="n"/>
       <c r="H29" s="18" t="n"/>
-      <c r="I29" s="41" t="n"/>
-      <c r="J29" s="18" t="n"/>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="18" t="n"/>
+      <c r="I29" s="105" t="n"/>
+      <c r="J29" s="106" t="n"/>
+      <c r="K29" s="107" t="n"/>
+      <c r="L29" s="106" t="n"/>
     </row>
     <row r="30" ht="19.05" customHeight="1" s="27">
-      <c r="A30" s="41" t="n">
+      <c r="A30" s="103" t="n">
         <v>13</v>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="104" t="inlineStr">
         <is>
           <t>Suelo y sustancias</t>
         </is>
       </c>
       <c r="C30" s="18" t="n"/>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D30" s="104" t="inlineStr">
         <is>
           <t>Combustibles y químicos con contención y hojas de seguridad</t>
         </is>
@@ -1852,22 +1907,22 @@
       <c r="F30" s="17" t="n"/>
       <c r="G30" s="17" t="n"/>
       <c r="H30" s="18" t="n"/>
-      <c r="I30" s="41" t="n"/>
-      <c r="J30" s="18" t="n"/>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="18" t="n"/>
+      <c r="I30" s="105" t="n"/>
+      <c r="J30" s="106" t="n"/>
+      <c r="K30" s="107" t="n"/>
+      <c r="L30" s="106" t="n"/>
     </row>
     <row r="31" ht="19.05" customHeight="1" s="27">
-      <c r="A31" s="41" t="n">
+      <c r="A31" s="103" t="n">
         <v>14</v>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="104" t="inlineStr">
         <is>
           <t>Suelo y sustancias</t>
         </is>
       </c>
       <c r="C31" s="18" t="n"/>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="104" t="inlineStr">
         <is>
           <t>Kit antiderrames disponible y completo</t>
         </is>
@@ -1876,22 +1931,22 @@
       <c r="F31" s="17" t="n"/>
       <c r="G31" s="17" t="n"/>
       <c r="H31" s="18" t="n"/>
-      <c r="I31" s="41" t="n"/>
-      <c r="J31" s="18" t="n"/>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="18" t="n"/>
+      <c r="I31" s="105" t="n"/>
+      <c r="J31" s="106" t="n"/>
+      <c r="K31" s="107" t="n"/>
+      <c r="L31" s="106" t="n"/>
     </row>
     <row r="32" ht="19.05" customHeight="1" s="27">
-      <c r="A32" s="41" t="n">
+      <c r="A32" s="103" t="n">
         <v>15</v>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="104" t="inlineStr">
         <is>
           <t>Suelo y sustancias</t>
         </is>
       </c>
       <c r="C32" s="18" t="n"/>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D32" s="104" t="inlineStr">
         <is>
           <t>Sin manchas de aceite o combustible en el suelo</t>
         </is>
@@ -1900,22 +1955,22 @@
       <c r="F32" s="17" t="n"/>
       <c r="G32" s="17" t="n"/>
       <c r="H32" s="18" t="n"/>
-      <c r="I32" s="41" t="n"/>
-      <c r="J32" s="18" t="n"/>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="18" t="n"/>
+      <c r="I32" s="105" t="n"/>
+      <c r="J32" s="106" t="n"/>
+      <c r="K32" s="107" t="n"/>
+      <c r="L32" s="106" t="n"/>
     </row>
     <row r="33" ht="19.05" customHeight="1" s="27">
-      <c r="A33" s="41" t="n">
+      <c r="A33" s="103" t="n">
         <v>16</v>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="104" t="inlineStr">
         <is>
           <t>Suelo y sustancias</t>
         </is>
       </c>
       <c r="C33" s="18" t="n"/>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D33" s="104" t="inlineStr">
         <is>
           <t>Mantenimiento de maquinaria sobre piso protegido</t>
         </is>
@@ -1924,22 +1979,22 @@
       <c r="F33" s="17" t="n"/>
       <c r="G33" s="17" t="n"/>
       <c r="H33" s="18" t="n"/>
-      <c r="I33" s="41" t="n"/>
-      <c r="J33" s="18" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="18" t="n"/>
+      <c r="I33" s="105" t="n"/>
+      <c r="J33" s="106" t="n"/>
+      <c r="K33" s="107" t="n"/>
+      <c r="L33" s="106" t="n"/>
     </row>
     <row r="34" ht="19.05" customHeight="1" s="27">
-      <c r="A34" s="41" t="n">
+      <c r="A34" s="103" t="n">
         <v>17</v>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="104" t="inlineStr">
         <is>
           <t>Flora y fauna</t>
         </is>
       </c>
       <c r="C34" s="18" t="n"/>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="104" t="inlineStr">
         <is>
           <t>Árboles y zonas verdes protegidos o con permiso vigente</t>
         </is>
@@ -1948,22 +2003,22 @@
       <c r="F34" s="17" t="n"/>
       <c r="G34" s="17" t="n"/>
       <c r="H34" s="18" t="n"/>
-      <c r="I34" s="41" t="n"/>
-      <c r="J34" s="18" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="18" t="n"/>
+      <c r="I34" s="105" t="n"/>
+      <c r="J34" s="106" t="n"/>
+      <c r="K34" s="107" t="n"/>
+      <c r="L34" s="106" t="n"/>
     </row>
     <row r="35" ht="19.05" customHeight="1" s="27">
-      <c r="A35" s="41" t="n">
+      <c r="A35" s="103" t="n">
         <v>18</v>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="104" t="inlineStr">
         <is>
           <t>Flora y fauna</t>
         </is>
       </c>
       <c r="C35" s="18" t="n"/>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="104" t="inlineStr">
         <is>
           <t>Sin captura ni afectación de fauna silvestre</t>
         </is>
@@ -1972,22 +2027,22 @@
       <c r="F35" s="17" t="n"/>
       <c r="G35" s="17" t="n"/>
       <c r="H35" s="18" t="n"/>
-      <c r="I35" s="41" t="n"/>
-      <c r="J35" s="18" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="18" t="n"/>
+      <c r="I35" s="105" t="n"/>
+      <c r="J35" s="106" t="n"/>
+      <c r="K35" s="107" t="n"/>
+      <c r="L35" s="106" t="n"/>
     </row>
     <row r="36" ht="19.05" customHeight="1" s="27">
-      <c r="A36" s="41" t="n">
+      <c r="A36" s="103" t="n">
         <v>19</v>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="104" t="inlineStr">
         <is>
           <t>Comunidad y entorno</t>
         </is>
       </c>
       <c r="C36" s="18" t="n"/>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D36" s="104" t="inlineStr">
         <is>
           <t>Cerramiento y señalización en buen estado</t>
         </is>
@@ -1996,22 +2051,22 @@
       <c r="F36" s="17" t="n"/>
       <c r="G36" s="17" t="n"/>
       <c r="H36" s="18" t="n"/>
-      <c r="I36" s="41" t="n"/>
-      <c r="J36" s="18" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="18" t="n"/>
+      <c r="I36" s="105" t="n"/>
+      <c r="J36" s="106" t="n"/>
+      <c r="K36" s="107" t="n"/>
+      <c r="L36" s="106" t="n"/>
     </row>
     <row r="37" ht="19.05" customHeight="1" s="27">
-      <c r="A37" s="41" t="n">
+      <c r="A37" s="103" t="n">
         <v>20</v>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B37" s="104" t="inlineStr">
         <is>
           <t>Comunidad y entorno</t>
         </is>
       </c>
       <c r="C37" s="18" t="n"/>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="104" t="inlineStr">
         <is>
           <t>Vías y andenes públicos limpios (barrido)</t>
         </is>
@@ -2020,22 +2075,22 @@
       <c r="F37" s="17" t="n"/>
       <c r="G37" s="17" t="n"/>
       <c r="H37" s="18" t="n"/>
-      <c r="I37" s="41" t="n"/>
-      <c r="J37" s="18" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="18" t="n"/>
+      <c r="I37" s="105" t="n"/>
+      <c r="J37" s="106" t="n"/>
+      <c r="K37" s="107" t="n"/>
+      <c r="L37" s="106" t="n"/>
     </row>
     <row r="38" ht="19.05" customHeight="1" s="27">
-      <c r="A38" s="41" t="n">
+      <c r="A38" s="103" t="n">
         <v>21</v>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="104" t="inlineStr">
         <is>
           <t>Comunidad y entorno</t>
         </is>
       </c>
       <c r="C38" s="18" t="n"/>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="104" t="inlineStr">
         <is>
           <t>Sin quejas de la comunidad abiertas sin atender</t>
         </is>
@@ -2044,22 +2099,22 @@
       <c r="F38" s="17" t="n"/>
       <c r="G38" s="17" t="n"/>
       <c r="H38" s="18" t="n"/>
-      <c r="I38" s="41" t="n"/>
-      <c r="J38" s="18" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="18" t="n"/>
+      <c r="I38" s="105" t="n"/>
+      <c r="J38" s="106" t="n"/>
+      <c r="K38" s="107" t="n"/>
+      <c r="L38" s="106" t="n"/>
     </row>
     <row r="39" ht="19.05" customHeight="1" s="27">
-      <c r="A39" s="41" t="n">
+      <c r="A39" s="103" t="n">
         <v>22</v>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B39" s="104" t="inlineStr">
         <is>
           <t>Comunidad y entorno</t>
         </is>
       </c>
       <c r="C39" s="18" t="n"/>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D39" s="104" t="inlineStr">
         <is>
           <t>Valla informativa de la obra con datos ambientales</t>
         </is>
@@ -2068,22 +2123,22 @@
       <c r="F39" s="17" t="n"/>
       <c r="G39" s="17" t="n"/>
       <c r="H39" s="18" t="n"/>
-      <c r="I39" s="41" t="n"/>
-      <c r="J39" s="18" t="n"/>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="18" t="n"/>
+      <c r="I39" s="105" t="n"/>
+      <c r="J39" s="106" t="n"/>
+      <c r="K39" s="107" t="n"/>
+      <c r="L39" s="106" t="n"/>
     </row>
     <row r="40" ht="25.95" customHeight="1" s="27">
-      <c r="A40" s="41" t="n">
+      <c r="A40" s="103" t="n">
         <v>23</v>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B40" s="104" t="inlineStr">
         <is>
           <t>Gestión y documentos</t>
         </is>
       </c>
       <c r="C40" s="18" t="n"/>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D40" s="104" t="inlineStr">
         <is>
           <t>Registros ambientales al día (residuos, consumos y manifiestos)</t>
         </is>
@@ -2092,22 +2147,22 @@
       <c r="F40" s="17" t="n"/>
       <c r="G40" s="17" t="n"/>
       <c r="H40" s="18" t="n"/>
-      <c r="I40" s="41" t="n"/>
-      <c r="J40" s="18" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="18" t="n"/>
+      <c r="I40" s="105" t="n"/>
+      <c r="J40" s="106" t="n"/>
+      <c r="K40" s="107" t="n"/>
+      <c r="L40" s="106" t="n"/>
     </row>
     <row r="41" ht="19.05" customHeight="1" s="27">
-      <c r="A41" s="41" t="n">
+      <c r="A41" s="103" t="n">
         <v>24</v>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B41" s="104" t="inlineStr">
         <is>
           <t>Gestión y documentos</t>
         </is>
       </c>
       <c r="C41" s="18" t="n"/>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="104" t="inlineStr">
         <is>
           <t>Permisos y autorizaciones ambientales vigentes en obra</t>
         </is>
@@ -2116,10 +2171,10 @@
       <c r="F41" s="17" t="n"/>
       <c r="G41" s="17" t="n"/>
       <c r="H41" s="18" t="n"/>
-      <c r="I41" s="41" t="n"/>
-      <c r="J41" s="18" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="18" t="n"/>
+      <c r="I41" s="105" t="n"/>
+      <c r="J41" s="106" t="n"/>
+      <c r="K41" s="107" t="n"/>
+      <c r="L41" s="106" t="n"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="27">
       <c r="A42" s="77" t="inlineStr">
@@ -2174,100 +2229,100 @@
       </c>
     </row>
     <row r="44" ht="24" customHeight="1" s="27">
-      <c r="A44" s="41" t="n">
+      <c r="A44" s="103" t="n">
         <v>1</v>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="17" t="n"/>
-      <c r="D44" s="17" t="n"/>
-      <c r="E44" s="17" t="n"/>
-      <c r="F44" s="18" t="n"/>
-      <c r="G44" s="16" t="n"/>
-      <c r="H44" s="17" t="n"/>
-      <c r="I44" s="18" t="n"/>
-      <c r="J44" s="16" t="n"/>
-      <c r="K44" s="18" t="n"/>
-      <c r="L44" s="26" t="n"/>
+      <c r="B44" s="107" t="n"/>
+      <c r="C44" s="108" t="n"/>
+      <c r="D44" s="108" t="n"/>
+      <c r="E44" s="108" t="n"/>
+      <c r="F44" s="106" t="n"/>
+      <c r="G44" s="107" t="n"/>
+      <c r="H44" s="108" t="n"/>
+      <c r="I44" s="106" t="n"/>
+      <c r="J44" s="107" t="n"/>
+      <c r="K44" s="106" t="n"/>
+      <c r="L44" s="109" t="n"/>
     </row>
     <row r="45" ht="24" customHeight="1" s="27">
-      <c r="A45" s="41" t="n">
+      <c r="A45" s="103" t="n">
         <v>2</v>
       </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="17" t="n"/>
-      <c r="D45" s="17" t="n"/>
-      <c r="E45" s="17" t="n"/>
-      <c r="F45" s="18" t="n"/>
-      <c r="G45" s="16" t="n"/>
-      <c r="H45" s="17" t="n"/>
-      <c r="I45" s="18" t="n"/>
-      <c r="J45" s="16" t="n"/>
-      <c r="K45" s="18" t="n"/>
-      <c r="L45" s="26" t="n"/>
+      <c r="B45" s="107" t="n"/>
+      <c r="C45" s="108" t="n"/>
+      <c r="D45" s="108" t="n"/>
+      <c r="E45" s="108" t="n"/>
+      <c r="F45" s="106" t="n"/>
+      <c r="G45" s="107" t="n"/>
+      <c r="H45" s="108" t="n"/>
+      <c r="I45" s="106" t="n"/>
+      <c r="J45" s="107" t="n"/>
+      <c r="K45" s="106" t="n"/>
+      <c r="L45" s="109" t="n"/>
     </row>
     <row r="46" ht="24" customHeight="1" s="27">
-      <c r="A46" s="41" t="n">
+      <c r="A46" s="103" t="n">
         <v>3</v>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="17" t="n"/>
-      <c r="D46" s="17" t="n"/>
-      <c r="E46" s="17" t="n"/>
-      <c r="F46" s="18" t="n"/>
-      <c r="G46" s="16" t="n"/>
-      <c r="H46" s="17" t="n"/>
-      <c r="I46" s="18" t="n"/>
-      <c r="J46" s="16" t="n"/>
-      <c r="K46" s="18" t="n"/>
-      <c r="L46" s="26" t="n"/>
+      <c r="B46" s="107" t="n"/>
+      <c r="C46" s="108" t="n"/>
+      <c r="D46" s="108" t="n"/>
+      <c r="E46" s="108" t="n"/>
+      <c r="F46" s="106" t="n"/>
+      <c r="G46" s="107" t="n"/>
+      <c r="H46" s="108" t="n"/>
+      <c r="I46" s="106" t="n"/>
+      <c r="J46" s="107" t="n"/>
+      <c r="K46" s="106" t="n"/>
+      <c r="L46" s="109" t="n"/>
     </row>
     <row r="47" ht="24" customHeight="1" s="27">
-      <c r="A47" s="41" t="n">
+      <c r="A47" s="103" t="n">
         <v>4</v>
       </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="17" t="n"/>
-      <c r="D47" s="17" t="n"/>
-      <c r="E47" s="17" t="n"/>
-      <c r="F47" s="18" t="n"/>
-      <c r="G47" s="16" t="n"/>
-      <c r="H47" s="17" t="n"/>
-      <c r="I47" s="18" t="n"/>
-      <c r="J47" s="16" t="n"/>
-      <c r="K47" s="18" t="n"/>
-      <c r="L47" s="26" t="n"/>
+      <c r="B47" s="107" t="n"/>
+      <c r="C47" s="108" t="n"/>
+      <c r="D47" s="108" t="n"/>
+      <c r="E47" s="108" t="n"/>
+      <c r="F47" s="106" t="n"/>
+      <c r="G47" s="107" t="n"/>
+      <c r="H47" s="108" t="n"/>
+      <c r="I47" s="106" t="n"/>
+      <c r="J47" s="107" t="n"/>
+      <c r="K47" s="106" t="n"/>
+      <c r="L47" s="109" t="n"/>
     </row>
     <row r="48" ht="24" customHeight="1" s="27">
-      <c r="A48" s="41" t="n">
+      <c r="A48" s="103" t="n">
         <v>5</v>
       </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="17" t="n"/>
-      <c r="D48" s="17" t="n"/>
-      <c r="E48" s="17" t="n"/>
-      <c r="F48" s="18" t="n"/>
-      <c r="G48" s="16" t="n"/>
-      <c r="H48" s="17" t="n"/>
-      <c r="I48" s="18" t="n"/>
-      <c r="J48" s="16" t="n"/>
-      <c r="K48" s="18" t="n"/>
-      <c r="L48" s="26" t="n"/>
+      <c r="B48" s="107" t="n"/>
+      <c r="C48" s="108" t="n"/>
+      <c r="D48" s="108" t="n"/>
+      <c r="E48" s="108" t="n"/>
+      <c r="F48" s="106" t="n"/>
+      <c r="G48" s="107" t="n"/>
+      <c r="H48" s="108" t="n"/>
+      <c r="I48" s="106" t="n"/>
+      <c r="J48" s="107" t="n"/>
+      <c r="K48" s="106" t="n"/>
+      <c r="L48" s="109" t="n"/>
     </row>
     <row r="49" ht="24" customHeight="1" s="27">
-      <c r="A49" s="41" t="n">
+      <c r="A49" s="103" t="n">
         <v>6</v>
       </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="17" t="n"/>
-      <c r="D49" s="17" t="n"/>
-      <c r="E49" s="17" t="n"/>
-      <c r="F49" s="18" t="n"/>
-      <c r="G49" s="16" t="n"/>
-      <c r="H49" s="17" t="n"/>
-      <c r="I49" s="18" t="n"/>
-      <c r="J49" s="16" t="n"/>
-      <c r="K49" s="18" t="n"/>
-      <c r="L49" s="26" t="n"/>
+      <c r="B49" s="107" t="n"/>
+      <c r="C49" s="108" t="n"/>
+      <c r="D49" s="108" t="n"/>
+      <c r="E49" s="108" t="n"/>
+      <c r="F49" s="106" t="n"/>
+      <c r="G49" s="107" t="n"/>
+      <c r="H49" s="108" t="n"/>
+      <c r="I49" s="106" t="n"/>
+      <c r="J49" s="107" t="n"/>
+      <c r="K49" s="106" t="n"/>
+      <c r="L49" s="109" t="n"/>
     </row>
     <row r="50" ht="16.5" customHeight="1" s="27">
       <c r="A50" s="77" t="inlineStr">
@@ -2288,18 +2343,18 @@
       <c r="L50" s="18" t="n"/>
     </row>
     <row r="51" ht="52.05" customHeight="1" s="27">
-      <c r="A51" s="40" t="n"/>
-      <c r="B51" s="25" t="n"/>
-      <c r="C51" s="25" t="n"/>
-      <c r="D51" s="25" t="n"/>
-      <c r="E51" s="25" t="n"/>
-      <c r="F51" s="25" t="n"/>
-      <c r="G51" s="25" t="n"/>
-      <c r="H51" s="25" t="n"/>
-      <c r="I51" s="25" t="n"/>
-      <c r="J51" s="25" t="n"/>
-      <c r="K51" s="25" t="n"/>
-      <c r="L51" s="22" t="n"/>
+      <c r="A51" s="110" t="n"/>
+      <c r="B51" s="98" t="n"/>
+      <c r="C51" s="98" t="n"/>
+      <c r="D51" s="98" t="n"/>
+      <c r="E51" s="98" t="n"/>
+      <c r="F51" s="98" t="n"/>
+      <c r="G51" s="98" t="n"/>
+      <c r="H51" s="98" t="n"/>
+      <c r="I51" s="98" t="n"/>
+      <c r="J51" s="98" t="n"/>
+      <c r="K51" s="98" t="n"/>
+      <c r="L51" s="99" t="n"/>
     </row>
     <row r="52" ht="16.5" customHeight="1" s="27">
       <c r="A52" s="77" t="inlineStr">
@@ -2348,20 +2403,20 @@
         </is>
       </c>
       <c r="B54" s="18" t="n"/>
-      <c r="C54" s="19" t="n"/>
-      <c r="D54" s="17" t="n"/>
-      <c r="E54" s="17" t="n"/>
-      <c r="F54" s="18" t="n"/>
+      <c r="C54" s="107" t="n"/>
+      <c r="D54" s="108" t="n"/>
+      <c r="E54" s="108" t="n"/>
+      <c r="F54" s="106" t="n"/>
       <c r="G54" s="82" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="H54" s="18" t="n"/>
-      <c r="I54" s="19" t="n"/>
-      <c r="J54" s="17" t="n"/>
-      <c r="K54" s="17" t="n"/>
-      <c r="L54" s="18" t="n"/>
+      <c r="I54" s="107" t="n"/>
+      <c r="J54" s="108" t="n"/>
+      <c r="K54" s="108" t="n"/>
+      <c r="L54" s="106" t="n"/>
     </row>
     <row r="55" ht="21" customHeight="1" s="27">
       <c r="A55" s="82" t="inlineStr">
@@ -2370,20 +2425,20 @@
         </is>
       </c>
       <c r="B55" s="18" t="n"/>
-      <c r="C55" s="19" t="n"/>
-      <c r="D55" s="17" t="n"/>
-      <c r="E55" s="17" t="n"/>
-      <c r="F55" s="18" t="n"/>
+      <c r="C55" s="107" t="n"/>
+      <c r="D55" s="108" t="n"/>
+      <c r="E55" s="108" t="n"/>
+      <c r="F55" s="106" t="n"/>
       <c r="G55" s="82" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="H55" s="18" t="n"/>
-      <c r="I55" s="19" t="n"/>
-      <c r="J55" s="17" t="n"/>
-      <c r="K55" s="17" t="n"/>
-      <c r="L55" s="18" t="n"/>
+      <c r="I55" s="107" t="n"/>
+      <c r="J55" s="108" t="n"/>
+      <c r="K55" s="108" t="n"/>
+      <c r="L55" s="106" t="n"/>
     </row>
     <row r="56" ht="21" customHeight="1" s="27">
       <c r="A56" s="82" t="inlineStr">
@@ -2392,20 +2447,20 @@
         </is>
       </c>
       <c r="B56" s="18" t="n"/>
-      <c r="C56" s="19" t="n"/>
-      <c r="D56" s="17" t="n"/>
-      <c r="E56" s="17" t="n"/>
-      <c r="F56" s="18" t="n"/>
+      <c r="C56" s="107" t="n"/>
+      <c r="D56" s="108" t="n"/>
+      <c r="E56" s="108" t="n"/>
+      <c r="F56" s="106" t="n"/>
       <c r="G56" s="82" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="H56" s="18" t="n"/>
-      <c r="I56" s="19" t="n"/>
-      <c r="J56" s="17" t="n"/>
-      <c r="K56" s="17" t="n"/>
-      <c r="L56" s="18" t="n"/>
+      <c r="I56" s="107" t="n"/>
+      <c r="J56" s="108" t="n"/>
+      <c r="K56" s="108" t="n"/>
+      <c r="L56" s="106" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -2419,6 +2474,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="174">
     <mergeCell ref="D35:H35"/>
     <mergeCell ref="A15:B15"/>
@@ -2461,8 +2517,8 @@
     <mergeCell ref="D23:H23"/>
     <mergeCell ref="D6:I6"/>
     <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B41:C41"/>
     <mergeCell ref="K13:L13"/>
-    <mergeCell ref="B41:C41"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="I30:J30"/>
